--- a/questionnaire_templates/015_language_practice_survey--questionnaire_templates.xlsx
+++ b/questionnaire_templates/015_language_practice_survey--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -827,8 +827,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -856,12 +856,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -873,12 +873,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -890,12 +890,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'several_times_a_week'}</t>
+          <t>several_times_a_week</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Several times a week'}</t>
+          <t>Several times a week</t>
         </is>
       </c>
     </row>
@@ -907,12 +907,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'almost_every_day'}</t>
+          <t>almost_every_day</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Almost every day'}</t>
+          <t>Almost every day</t>
         </is>
       </c>
     </row>
@@ -924,12 +924,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'grammar'}</t>
+          <t>grammar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Grammar'}</t>
+          <t>Grammar</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'vocab'}</t>
+          <t>vocab</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Vocab'}</t>
+          <t>Vocab</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'pronunciation'}</t>
+          <t>pronunciation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Pronunciation'}</t>
+          <t>Pronunciation</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'listening'}</t>
+          <t>listening</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Listening'}</t>
+          <t>Listening</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Not at all'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
